--- a/output/laminas_comunales/comunal_o_ocup_a_2020_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2020_la_araucania.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>38.329927491883</v>
+        <v>58.8434412873001</v>
       </c>
     </row>
     <row r="3">
@@ -399,52 +399,52 @@
         </is>
       </c>
       <c r="C3">
-        <v>36.6449702877175</v>
+        <v>57.3873005226237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="C4">
-        <v>34.7228736710444</v>
+        <v>52.458671475804</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C5">
-        <v>34.3394542012344</v>
+        <v>52.0669369584228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C6">
-        <v>34.023799880422</v>
+        <v>51.100046037169</v>
       </c>
     </row>
     <row r="7">
@@ -459,172 +459,172 @@
         </is>
       </c>
       <c r="C7">
-        <v>33.924532793715</v>
+        <v>50.9289564882557</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C8">
-        <v>32.9875756793205</v>
+        <v>50.5465512719643</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C9">
-        <v>32.8967258735012</v>
+        <v>49.6149670941041</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C10">
-        <v>32.3502817502514</v>
+        <v>49.4672478508294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C11">
-        <v>30.6361825908328</v>
+        <v>49.238842928696</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C12">
-        <v>30.2480008947045</v>
+        <v>48.6885192606647</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C13">
-        <v>30.1542722290484</v>
+        <v>48.4241048915784</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C14">
-        <v>29.9434539264901</v>
+        <v>48.4048631107455</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C15">
-        <v>29.9064606811454</v>
+        <v>47.9265120709235</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C16">
-        <v>29.3389925311749</v>
+        <v>47.0710757207108</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C17">
-        <v>29.0167253670903</v>
+        <v>46.5692999926237</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C18">
-        <v>28.8785296781098</v>
+        <v>46.1880417870638</v>
       </c>
     </row>
     <row r="19">
@@ -639,217 +639,3097 @@
         </is>
       </c>
       <c r="C19">
-        <v>27.6929987976799</v>
+        <v>46.013397356097</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C20">
-        <v>27.5805724588686</v>
+        <v>45.8916488042702</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C21">
-        <v>26.907018935025</v>
+        <v>45.7558768564965</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C22">
-        <v>25.4970836314751</v>
+        <v>45.173927468545</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C23">
-        <v>25.3601427514471</v>
+        <v>44.2453136091563</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Ercilla</t>
         </is>
       </c>
       <c r="C24">
-        <v>25.2160194174757</v>
+        <v>44.123764950598</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C25">
-        <v>24.5050338137642</v>
+        <v>43.8056171967812</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C26">
-        <v>24.4874048037493</v>
+        <v>43.4524722605717</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C27">
-        <v>24.3039571718412</v>
+        <v>43.2239646160032</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C28">
-        <v>23.9835164835165</v>
+        <v>43.1670753167959</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C29">
-        <v>23.0275761973875</v>
+        <v>43.1300213149697</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C30">
-        <v>22.6324799626488</v>
+        <v>42.9596018735363</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C31">
-        <v>21.974750469414</v>
+        <v>42.8721377127539</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C32">
-        <v>19.1326147246472</v>
+        <v>42.7101399005665</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>42.5442742799521</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>42.2630095552348</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>41.8591859185919</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>41.3906354659579</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>41.0347577963512</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>40.3063316347449</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>40.186436520149</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>39.986709313704</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>39.7679633421078</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>39.6667788623359</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>39.3993724787091</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>39.3156683737846</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>38.9984587968983</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>38.8118123564261</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>38.778582854992</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>38.7419464225161</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>38.5695903924512</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>38.329927491883</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>38.107482643353</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>37.4967693997545</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>37.1005005775895</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>36.6449702877175</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>36.5321017219751</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>36.5043775357677</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>36.2492599171107</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>36.0612460401267</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>36.0324729392173</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>35.8209759316875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>35.7391029690461</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>35.6689781218083</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>35.270285747008</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>35.2512337371018</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>35.1675440795521</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>34.9521053900616</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>34.7228736710444</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>34.3679138321995</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>34.3394542012344</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>34.023799880422</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>33.9693866997621</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>33.924532793715</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>33.5362455664169</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>33.5036496350365</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>33.0538891452597</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>33.0109022423079</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>32.9875756793205</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>32.9109598403456</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>32.8967258735012</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>32.7885708101088</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>9116</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Saavedra</t>
         </is>
       </c>
-      <c r="C33">
+      <c r="C81">
+        <v>32.7014391116955</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>32.5642332523066</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>32.4962438291479</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>32.4873679375287</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>32.3502817502514</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>32.2541743970315</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>32.2532938962087</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>32.039941026672</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>31.9145239749826</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>31.857219538379</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>31.737963333143</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>31.3817481503151</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>31.2490110879858</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>31.1400889242816</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>30.8325493885231</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>30.6955425690386</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>30.6696874280009</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>30.6361825908328</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>30.6025316455696</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>30.5309948301686</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>30.4560728655436</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>30.2480008947045</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>30.1542722290484</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>30.1256348569901</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>30.0447973936062</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>29.9434539264901</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>29.9064606811454</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>29.7792984402934</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>29.3936522974893</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>29.3389925311749</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>29.2880658436214</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>29.222544400145</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>29.0575354229283</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>29.0385112432153</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>29.0215421783773</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>29.0167253670903</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>28.8785296781098</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>28.364434687157</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>28.1493333333333</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>28.0931685454299</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>27.9065200314218</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>27.7687222674998</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>27.6929987976799</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>27.5805724588686</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>27.5426343053373</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>27.4439498846027</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>27.3637951741457</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>27.2754137115839</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>27.2736613830437</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>27.1623419827013</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>27.1080117182524</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>27.1061305207647</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>26.9401758963951</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>26.907018935025</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>26.8145813126415</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>26.5061563454579</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>26.5051903114187</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>26.4614390174928</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>26.283277940041</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>26.1434370771313</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>26.1385115829267</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>26.1051233989378</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>25.9893313484679</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>25.9590505118686</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>25.4970836314751</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>25.3601427514471</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>25.2771402427133</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>25.2160194174757</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>25.0155251141553</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>24.8676378446115</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>24.8566801387336</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>24.7583304901626</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>24.7279803033913</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>24.6951219512195</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>24.6347871781398</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>24.5050338137642</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>24.4874048037493</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>24.3922788977585</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>24.3039571718412</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>24.2017774851876</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>23.9960147148988</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>23.9835164835165</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>23.6001317523057</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>23.5040248278537</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>23.3996683250415</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>23.0275761973875</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>22.9684351914036</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>22.9071537290715</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>22.8124680372302</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>22.6753496316857</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>22.6324799626488</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>22.1082834331337</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>22.0130439548394</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>21.974750469414</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>21.4684052979046</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>21.2264896475423</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>20.874396621078</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>20.7248319291975</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>20.6052612295743</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>20.5373604292254</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>20.2564102564103</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>20.0042198948863</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>19.8369565217391</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>19.796395652772</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>19.7168531705663</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>19.306720136104</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>19.2481787962374</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>19.1326147246472</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C189">
         <v>18.8137318713597</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>18.5082399698496</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>18.477965917725</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>17.938479739722</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>17.8250396094028</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>9.741173922460471</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>9.011320140076551</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>8.98339845211898</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>8.796674843281551</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>8.527268453220501</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>8.49195218059173</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>8.27334376630151</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>8.124777036854089</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>7.8955272155993</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>7.86209830486288</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>7.34038867365901</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>7.28798185941043</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>7.1568931637191</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>7.14758073404607</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>7.01116204903329</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>6.88504572045209</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>6.84578758138179</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>6.28428525330752</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>6.10136876883419</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>6.05034203360563</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>5.98416026088982</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>5.79148766345048</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>5.71074566343771</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>5.67467652495379</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>5.38945712037766</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>4.8758865248227</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>4.54267547077525</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>4.25250924458531</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>4.14525139664805</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>4.06395736175883</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>3.21755994358251</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>3.1965762922584</v>
       </c>
     </row>
   </sheetData>
